--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -983,9 +983,9 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -1535,9 +1535,9 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
 [CONSIDER]</t>
@@ -2087,9 +2087,9 @@
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
 [CONSIDER]</t>

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -810,12 +810,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-52% pred | 0% hist
-[PINNED]</t>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+38% pred | 0% hist
+[DROP]</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
           <t>Back Body Blaze
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
           <t>FIT
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -882,8 +882,8 @@
       <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
-17% pred | 17% hist
+Siddhartha Kusuma
+19% pred | 19% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -900,7 +900,7 @@
           <t>Mat 57
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -916,7 +916,7 @@
           <t>Mat 57
 Pushyank Nahar
 43% pred | 43% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -940,7 +940,7 @@
           <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -988,7 +988,7 @@
           <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -996,7 +996,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -1012,7 +1012,7 @@
           <t>Recovery
 Shruti Kulkarni
 10% pred | 10% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1020,7 +1020,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1028,7 +1028,7 @@
           <t>FIT
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -1036,7 +1036,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1063,7 +1063,7 @@
           <t>Back Body Blaze
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
@@ -1362,12 +1362,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-52% pred | 0% hist
-[PINNED]</t>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+38% pred | 0% hist
+[DROP]</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
           <t>Back Body Blaze
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
           <t>FIT
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -1434,8 +1434,8 @@
       <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
-17% pred | 17% hist
+Siddhartha Kusuma
+19% pred | 19% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1452,7 +1452,7 @@
           <t>Mat 57
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1468,7 +1468,7 @@
           <t>Mat 57
 Pushyank Nahar
 43% pred | 43% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1492,7 +1492,7 @@
           <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -1540,7 +1540,7 @@
           <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -1548,7 +1548,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -1564,7 +1564,7 @@
           <t>Recovery
 Shruti Kulkarni
 10% pred | 10% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1572,7 +1572,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1580,7 +1580,7 @@
           <t>FIT
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -1588,7 +1588,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1615,7 +1615,7 @@
           <t>Back Body Blaze
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>
@@ -1914,12 +1914,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-52% pred | 0% hist
-[PINNED]</t>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+38% pred | 0% hist
+[DROP]</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
           <t>Back Body Blaze
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
           <t>FIT
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H10" s="6" t="n"/>
@@ -1986,8 +1986,8 @@
       <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
-17% pred | 17% hist
+Siddhartha Kusuma
+19% pred | 19% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2004,7 +2004,7 @@
           <t>Mat 57
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -2020,7 +2020,7 @@
           <t>Mat 57
 Pushyank Nahar
 43% pred | 43% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -2044,7 +2044,7 @@
           <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -2092,7 +2092,7 @@
           <t>Mat 57
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
@@ -2100,7 +2100,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -2116,7 +2116,7 @@
           <t>Recovery
 Shruti Kulkarni
 10% pred | 10% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -2124,7 +2124,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -2132,7 +2132,7 @@
           <t>FIT
 Pushyank Nahar
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -2140,7 +2140,7 @@
           <t>Recovery
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -2167,7 +2167,7 @@
           <t>Back Body Blaze
 Shruti Kulkarni
 38% pred | 0% hist
-[CONSIDER]</t>
+[PROTECT]</t>
         </is>
       </c>
       <c r="E15" s="6" t="n"/>

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -654,9 +654,9 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Siddhartha Kusuma
-0% pred | 0% hist
+          <t>Cardio Barre
+Shruti Kulkarni
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -759,8 +759,8 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Siddhartha Kusuma
+          <t>Cardio Barre Plus
+Pushyank Nahar
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -768,7 +768,14 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -810,12 +817,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Suresh
-38% pred | 0% hist
-[DROP]</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+52% pred | 0% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
@@ -851,7 +858,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Back Body Blaze Express
 Shruti Kulkarni
 38% pred | 0% hist
 [DROP]</t>
@@ -869,22 +876,57 @@
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
-19% pred | 19% hist
-[CONSIDER]</t>
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -892,55 +934,55 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-43% pred | 43% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+19% pred | 19% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Suresh
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Suresh
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>FIT
+Pushyank Nahar
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Chaitanya Nahar
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -948,53 +990,53 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Pushyank Nahar
+26% pred | 26% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Shruti Kulkarni
+Pushyank Nahar
 38% pred | 0% hist
 [PROTECT]</t>
         </is>
@@ -1004,25 +1046,11 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-10% pred | 10% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>FIT
@@ -1031,45 +1059,10 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1085,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1206,9 +1199,9 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Siddhartha Kusuma
-0% pred | 0% hist
+          <t>Cardio Barre
+Shruti Kulkarni
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1311,8 +1304,8 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Siddhartha Kusuma
+          <t>Cardio Barre Plus
+Pushyank Nahar
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -1320,7 +1313,14 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1362,12 +1362,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Suresh
-38% pred | 0% hist
-[DROP]</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+52% pred | 0% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Back Body Blaze Express
 Shruti Kulkarni
 38% pred | 0% hist
 [DROP]</t>
@@ -1421,22 +1421,57 @@
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
-19% pred | 19% hist
-[CONSIDER]</t>
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -1444,55 +1479,55 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-43% pred | 43% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+19% pred | 19% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Suresh
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Suresh
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>FIT
+Pushyank Nahar
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Chaitanya Nahar
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -1500,53 +1535,53 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Pushyank Nahar
+26% pred | 26% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Shruti Kulkarni
+Pushyank Nahar
 38% pred | 0% hist
 [PROTECT]</t>
         </is>
@@ -1556,25 +1591,11 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-10% pred | 10% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>FIT
@@ -1583,45 +1604,10 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1637,7 +1623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1758,9 +1744,9 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Siddhartha Kusuma
-0% pred | 0% hist
+          <t>Cardio Barre
+Shruti Kulkarni
+38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1863,8 +1849,8 @@
       <c r="C7" s="6" t="n"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Barre 57
-Siddhartha Kusuma
+          <t>Cardio Barre Plus
+Pushyank Nahar
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
@@ -1872,7 +1858,14 @@
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1914,12 +1907,12 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Suresh
-38% pred | 0% hist
-[DROP]</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+52% pred | 0% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1948,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>FIT
+          <t>Back Body Blaze Express
 Shruti Kulkarni
 38% pred | 0% hist
 [DROP]</t>
@@ -1973,22 +1966,57 @@
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
-19% pred | 19% hist
-[CONSIDER]</t>
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+38% pred | 0% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -1996,55 +2024,55 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-43% pred | 43% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+19% pred | 19% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Suresh
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Suresh
 38% pred | 0% hist
 [CONSIDER]</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>FIT
+Pushyank Nahar
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Chaitanya Nahar
+38% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -2052,53 +2080,53 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+38% pred | 0% hist
+[PROTECT]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+38% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
-Siddhartha Kusuma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Pushyank Nahar
+26% pred | 26% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Recovery
-Shruti Kulkarni
+Pushyank Nahar
 38% pred | 0% hist
 [PROTECT]</t>
         </is>
@@ -2108,25 +2136,11 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-10% pred | 10% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
       <c r="D14" s="5" t="inlineStr">
         <is>
           <t>FIT
@@ -2135,45 +2149,10 @@
 [PROTECT]</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Iteration 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Iteration 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Max Score" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trainer Hours" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Variety" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,10 +52,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="00374151"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <color rgb="000C4A6E"/>
       <sz val="9"/>
     </font>
@@ -64,7 +60,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -94,11 +90,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F5"/>
       </patternFill>
     </fill>
     <fill>
@@ -138,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -163,9 +154,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -533,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -549,7 +537,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Main  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -612,7 +600,7 @@
         <is>
           <t>Barre 57
 Pushyank Nahar
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -624,7 +612,14 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+63% pred | 63% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Barre 57
@@ -654,13 +649,20 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pushyank Nahar
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
@@ -675,7 +677,7 @@
         <is>
           <t>Back Body Blaze
 Pushyank Nahar
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -683,34 +685,20 @@
         <is>
           <t>Back Body Blaze
 Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Unknown Class
-Pushyank Nahar
-38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
+20% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-19% pred | 19% hist
-[PINNED]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Shruti Kulkarni
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Barre 57
@@ -732,19 +720,12 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 38% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -757,25 +738,18 @@
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+Kajol Kanchan
+77% pred | 77% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -800,133 +774,126 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Kajol Kanchan
-31% pred | 31% hist
-[PINNED]</t>
+Shruti Suresh
+15% pred | 15% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-52% pred | 0% hist
+68% pred | 68% hist
 [PINNED]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+20% pred | 0% hist
+[DROP]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Shruti Kulkarni
-38% pred | 0% hist
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+56% pred | 56% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pushyank Nahar
+20% pred | 0% hist
 [DROP]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
         </is>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -934,55 +901,55 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-19% pred | 19% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-38% pred | 0% hist
-[CONSIDER]</t>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -990,55 +957,55 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+38% pred | 38% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+77% pred | 77% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Pushyank Nahar
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -1046,23 +1013,79 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+46% pred | 46% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+Shruti Kulkarni
+69% pred | 69% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1078,7 +1101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1117,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Iteration 2  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1180,7 @@
         <is>
           <t>Barre 57
 Pushyank Nahar
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -1169,7 +1192,14 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+63% pred | 63% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1199,13 +1229,20 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pushyank Nahar
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
@@ -1220,7 +1257,7 @@
         <is>
           <t>Back Body Blaze
 Pushyank Nahar
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -1228,34 +1265,20 @@
         <is>
           <t>Back Body Blaze
 Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Unknown Class
-Pushyank Nahar
-38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
+20% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-19% pred | 19% hist
-[PINNED]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Shruti Kulkarni
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1277,19 +1300,12 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 38% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -1302,25 +1318,18 @@
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+Kajol Kanchan
+77% pred | 77% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1345,133 +1354,126 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Kajol Kanchan
-31% pred | 31% hist
-[PINNED]</t>
+Shruti Suresh
+15% pred | 15% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-52% pred | 0% hist
+68% pred | 68% hist
 [PINNED]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+20% pred | 0% hist
+[DROP]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Shruti Kulkarni
-38% pred | 0% hist
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+56% pred | 56% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pushyank Nahar
+20% pred | 0% hist
 [DROP]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
         </is>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -1479,55 +1481,55 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-19% pred | 19% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-38% pred | 0% hist
-[CONSIDER]</t>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -1535,55 +1537,55 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+38% pred | 38% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+77% pred | 77% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Pushyank Nahar
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -1591,23 +1593,79 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+46% pred | 46% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+Shruti Kulkarni
+69% pred | 69% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1623,7 +1681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1639,7 +1697,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Iteration 3  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1760,7 @@
         <is>
           <t>Barre 57
 Pushyank Nahar
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -1714,7 +1772,14 @@
 [PINNED]</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+63% pred | 63% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1744,13 +1809,20 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n"/>
+          <t>Barre 57
+Kajol Kanchan
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pushyank Nahar
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="F4" s="6" t="n"/>
       <c r="G4" s="6" t="n"/>
       <c r="H4" s="6" t="n"/>
@@ -1765,7 +1837,7 @@
         <is>
           <t>Back Body Blaze
 Pushyank Nahar
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -1773,34 +1845,20 @@
         <is>
           <t>Back Body Blaze
 Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Unknown Class
-Pushyank Nahar
-38% pred | 0% hist
-[DROP]</t>
-        </is>
-      </c>
+20% pred | 0% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-19% pred | 19% hist
-[PINNED]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Shruti Kulkarni
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1822,19 +1880,12 @@
       <c r="D6" s="6" t="n"/>
       <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 38% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
-52% pred | 0% hist
+20% pred | 0% hist
 [PINNED]</t>
         </is>
       </c>
@@ -1847,25 +1898,18 @@
       </c>
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>FIT
-Siddhartha Kusuma
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+Kajol Kanchan
+77% pred | 77% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n"/>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1890,133 +1934,126 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-52% pred | 0% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Kajol Kanchan
-31% pred | 31% hist
-[PINNED]</t>
+Shruti Suresh
+15% pred | 15% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-52% pred | 0% hist
+68% pred | 68% hist
 [PINNED]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Kulkarni
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Shruti Suresh
+20% pred | 0% hist
+[DROP]</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Shruti Kulkarni
-38% pred | 0% hist
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+56% pred | 56% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57 Express
+Pushyank Nahar
+20% pred | 0% hist
 [DROP]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-50% pred | 50% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
         </is>
       </c>
       <c r="H11" s="6" t="n"/>
@@ -2024,55 +2061,55 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-19% pred | 19% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 31% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Suresh
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-38% pred | 0% hist
-[CONSIDER]</t>
+          <t>Barre 57
+Shruti Kulkarni
+20% pred | 0% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
@@ -2080,55 +2117,55 @@
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+38% pred | 38% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+77% pred | 77% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+31% pred | 31% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Karan Bhatia
+38% pred | 38% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Mat 57
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Shruti Kulkarni
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-38% pred | 0% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-26% pred | 26% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
+Pushyank Nahar
+20% pred | 0% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="H13" s="6" t="n"/>
@@ -2136,23 +2173,79 @@
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+46% pred | 46% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>FIT
-Pushyank Nahar
-38% pred | 0% hist
-[PROTECT]</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
+Shruti Kulkarni
+69% pred | 69% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+20% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
+Siddhartha Kusuma
 35% pred | 0% hist
 []</t>
         </is>
@@ -646,11 +646,11 @@
 []</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Shruti Kulkarni
-31% pred | 0% hist
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -697,19 +697,12 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
 61% pred | 0% hist
 []</t>
         </is>
@@ -719,7 +712,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -727,20 +720,20 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -748,23 +741,44 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -772,7 +786,7 @@
 []</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
@@ -780,7 +794,7 @@
 []</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -788,8 +802,8 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -797,34 +811,13 @@
 []</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -835,17 +828,17 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Chaitanya Nahar
-20% pred | 0% hist
+          <t>Back Body Blaze
+Shruti Kulkarni
+50% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -853,11 +846,11 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-28% pred | 0% hist
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -866,93 +859,72 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 0% hist
+          <t>FIT
+Siddhartha Kusuma
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -962,70 +934,49 @@
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Siddhartha Kusuma
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
@@ -1034,41 +985,104 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n"/>
+Siddhartha Kusuma
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Kajol Kanchan
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Pushyank Nahar
@@ -1076,7 +1090,7 @@
 []</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Chaitanya Nahar
@@ -1084,24 +1098,24 @@
 []</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Chaitanya Nahar
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
@@ -1109,7 +1123,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
@@ -1117,31 +1131,31 @@
 []</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1157,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1252,7 +1266,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
+Siddhartha Kusuma
 35% pred | 0% hist
 []</t>
         </is>
@@ -1282,11 +1296,11 @@
 []</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Shruti Kulkarni
-31% pred | 0% hist
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1333,19 +1347,12 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
 61% pred | 0% hist
 []</t>
         </is>
@@ -1355,7 +1362,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -1363,20 +1370,20 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -1384,23 +1391,44 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -1408,7 +1436,7 @@
 []</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
@@ -1416,7 +1444,7 @@
 []</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -1424,8 +1452,8 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -1433,34 +1461,13 @@
 []</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -1471,17 +1478,17 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Chaitanya Nahar
-20% pred | 0% hist
+          <t>Back Body Blaze
+Shruti Kulkarni
+50% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -1489,11 +1496,11 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-28% pred | 0% hist
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1502,93 +1509,72 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 0% hist
+          <t>FIT
+Siddhartha Kusuma
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1598,70 +1584,49 @@
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Siddhartha Kusuma
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
@@ -1670,41 +1635,104 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n"/>
+Siddhartha Kusuma
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Kajol Kanchan
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Pushyank Nahar
@@ -1712,7 +1740,7 @@
 []</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Chaitanya Nahar
@@ -1720,24 +1748,24 @@
 []</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Chaitanya Nahar
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
@@ -1745,7 +1773,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
@@ -1753,31 +1781,31 @@
 []</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1793,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1888,7 +1916,7 @@
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
+Siddhartha Kusuma
 35% pred | 0% hist
 []</t>
         </is>
@@ -1918,11 +1946,11 @@
 []</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Shruti Kulkarni
-31% pred | 0% hist
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+20% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -1969,19 +1997,12 @@
 []</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
 61% pred | 0% hist
 []</t>
         </is>
@@ -1991,7 +2012,7 @@
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>
@@ -1999,20 +2020,20 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B7" s="5" t="n"/>
@@ -2020,23 +2041,44 @@
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+80% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -2044,7 +2086,7 @@
 []</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
@@ -2052,7 +2094,7 @@
 []</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -2060,8 +2102,8 @@
 []</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -2069,34 +2111,13 @@
 []</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
       <c r="G9" s="5" t="n"/>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="B10" s="5" t="n"/>
@@ -2107,17 +2128,17 @@
       <c r="G10" s="5" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Express
-Chaitanya Nahar
-20% pred | 0% hist
+          <t>Back Body Blaze
+Shruti Kulkarni
+50% pred | 0% hist
 []</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>16:00</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B11" s="5" t="n"/>
@@ -2125,11 +2146,11 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-28% pred | 0% hist
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+43% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2138,93 +2159,72 @@
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
       <c r="G12" s="5" t="n"/>
-      <c r="H12" s="5" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+20% pred | 0% hist
+[]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C13" s="5" t="n"/>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+28% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 0% hist
+          <t>FIT
+Siddhartha Kusuma
+45% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 0% hist
 []</t>
         </is>
       </c>
@@ -2234,70 +2234,49 @@
       <c r="H14" s="5" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+47% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Siddhartha Kusuma
+46% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
 Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
+61% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
@@ -2306,41 +2285,104 @@
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+40% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n"/>
+Siddhartha Kusuma
+31% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 0% hist
+[]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre Plus
+Kajol Kanchan
+26% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+22% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+32% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57 Express
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Pushyank Nahar
@@ -2348,7 +2390,7 @@
 []</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Chaitanya Nahar
@@ -2356,24 +2398,24 @@
 []</t>
         </is>
       </c>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-48% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Chaitanya Nahar
+30% pred | 0% hist
+[]</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
@@ -2381,7 +2423,7 @@
 []</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
@@ -2389,31 +2431,31 @@
 []</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57 Express
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
 Kajol Kanchan
 20% pred | 0% hist
 []</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -43,6 +43,10 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="006B21A8"/>
       <sz val="9"/>
     </font>
@@ -50,10 +54,6 @@
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -79,7 +79,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAFAFA"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,12 +89,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -143,15 +143,15 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -596,44 +596,51 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-63% pred | 0% hist
-[]</t>
+63% pred | 63% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -642,8 +649,8 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-9% pred | 0% hist
-[]</t>
+9% pred | 9% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -651,24 +658,24 @@
           <t>Back Body Blaze
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -677,37 +684,37 @@
         <is>
           <t>FIT
 Pushyank Nahar
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -715,20 +722,20 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -736,83 +743,90 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+14% pred | 14% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Kajol Kanchan
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+Siddhartha Kusuma
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -820,41 +834,41 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Siddhartha Kusuma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -862,18 +876,18 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -883,20 +897,20 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -908,30 +922,30 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -939,23 +953,23 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -964,26 +978,33 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
+46% pred | 46% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -992,37 +1013,37 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-31% pred | 0% hist
-[]</t>
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Kajol Kanchan
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1030,64 +1051,64 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+26% pred | 26% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Pushyank Nahar
-54% pred | 0% hist
-[]</t>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -1095,14 +1116,14 @@
           <t>Recovery
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
@@ -1111,30 +1132,30 @@
         <is>
           <t>Recovery
 Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+66% pred | 66% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1142,20 +1163,20 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Kajol Kanchan
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1246,44 +1267,51 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-63% pred | 0% hist
-[]</t>
+63% pred | 63% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -1292,8 +1320,8 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-9% pred | 0% hist
-[]</t>
+9% pred | 9% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1301,24 +1329,24 @@
           <t>Back Body Blaze
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1327,37 +1355,37 @@
         <is>
           <t>FIT
 Pushyank Nahar
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -1365,20 +1393,20 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1386,83 +1414,90 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+14% pred | 14% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Kajol Kanchan
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+Siddhartha Kusuma
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1470,41 +1505,41 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Siddhartha Kusuma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1512,18 +1547,18 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -1533,20 +1568,20 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1558,30 +1593,30 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1589,23 +1624,23 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -1614,26 +1649,33 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
+46% pred | 46% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -1642,37 +1684,37 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-31% pred | 0% hist
-[]</t>
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Kajol Kanchan
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1680,64 +1722,64 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+26% pred | 26% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Pushyank Nahar
-54% pred | 0% hist
-[]</t>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -1745,14 +1787,14 @@
           <t>Recovery
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
@@ -1761,30 +1803,30 @@
         <is>
           <t>Recovery
 Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+66% pred | 66% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1792,20 +1834,20 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Kajol Kanchan
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1896,54 +1938,61 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-63% pred | 0% hist
-[]</t>
+63% pred | 63% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-9% pred | 0% hist
-[]</t>
+          <t>Cardio Barre Plus
+Shruti Kulkarni
+9% pred | 9% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1951,24 +2000,24 @@
           <t>Back Body Blaze
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1977,37 +2026,37 @@
         <is>
           <t>FIT
 Pushyank Nahar
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -2015,20 +2064,20 @@
           <t>09:15</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -2036,83 +2085,90 @@
           <t>10:00</t>
         </is>
       </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="7" t="n"/>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
+      <c r="F7" s="7" t="n"/>
+      <c r="G7" s="7" t="n"/>
       <c r="H7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
       <c r="G8" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+14% pred | 14% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Kajol Kanchan
-80% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
+Siddhartha Kusuma
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n"/>
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="n"/>
-      <c r="H9" s="5" t="n"/>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -2120,41 +2176,41 @@
           <t>11:15</t>
         </is>
       </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Siddhartha Kusuma
-43% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -2162,18 +2218,18 @@
           <t>12:30</t>
         </is>
       </c>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -2183,20 +2239,20 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="n"/>
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -2208,30 +2264,30 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
+45% pred | 45% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-18% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2239,23 +2295,23 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="7" t="n"/>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -2264,26 +2320,33 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="8" t="inlineStr">
+46% pred | 46% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -2292,37 +2355,37 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-31% pred | 0% hist
-[]</t>
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
 Kajol Kanchan
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -2330,64 +2393,64 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
+      <c r="B18" s="7" t="n"/>
       <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre Plus
 Kajol Kanchan
-26% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+26% pred | 26% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-32% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
       <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Pushyank Nahar
-54% pred | 0% hist
-[]</t>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -2395,14 +2458,14 @@
           <t>Recovery
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
@@ -2411,30 +2474,30 @@
         <is>
           <t>Recovery
 Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
+66% pred | 66% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -2442,20 +2505,20 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
+      <c r="B22" s="7" t="n"/>
       <c r="C22" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Kajol Kanchan
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -537,7 +537,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Kenkere House  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -550,43 +550,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 58% hist
+55% pred | 55% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -616,7 +616,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-63% pred | 63% hist
+64% pred | 64% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -624,7 +624,7 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-35% pred | 35% hist
+36% pred | 36% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -632,7 +632,7 @@
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 36% hist
+38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -666,7 +666,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-43% pred | 43% hist
+40% pred | 40% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -797,7 +797,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-44% pred | 44% hist
+42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -813,7 +813,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-30% pred | 30% hist
+31% pred | 31% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -938,7 +938,7 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-18% pred | 18% hist
+20% pred | 20% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -978,7 +978,7 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 46% hist
+23% pred | 23% hist
 [DROP]</t>
         </is>
       </c>
@@ -1140,7 +1140,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-66% pred | 66% hist
+67% pred | 67% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1148,7 +1148,7 @@
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 46% hist
+47% pred | 47% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1208,7 +1208,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1221,43 +1221,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 58% hist
+55% pred | 55% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1287,7 +1287,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-63% pred | 63% hist
+64% pred | 64% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1295,7 +1295,7 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-35% pred | 35% hist
+36% pred | 36% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1303,7 +1303,7 @@
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 36% hist
+38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1333,12 +1333,12 @@
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-43% pred | 43% hist
-[PROTECT_EXACT]</t>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
@@ -1468,7 +1468,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-44% pred | 44% hist
+42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1480,14 +1480,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="E9" s="7" t="n"/>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1528,7 +1521,14 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="9" t="inlineStr">
@@ -1555,8 +1555,8 @@
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Chaitanya Nahar
+          <t>Cardio Barre
+Siddhartha Kusuma
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1605,15 +1605,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-18% pred | 18% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
@@ -1649,7 +1649,7 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 46% hist
+23% pred | 23% hist
 [DROP]</t>
         </is>
       </c>
@@ -1662,14 +1662,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
@@ -1811,7 +1804,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-66% pred | 66% hist
+67% pred | 67% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1819,7 +1812,7 @@
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 46% hist
+47% pred | 47% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1879,7 +1872,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1892,43 +1885,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1943,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 58% hist
+55% pred | 55% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1958,7 +1951,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-63% pred | 63% hist
+64% pred | 64% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1966,7 +1959,7 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-35% pred | 35% hist
+36% pred | 36% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1974,7 +1967,7 @@
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 36% hist
+38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2008,7 +2001,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-43% pred | 43% hist
+40% pred | 40% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2139,7 +2132,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-44% pred | 44% hist
+42% pred | 42% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2155,7 +2148,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-30% pred | 30% hist
+31% pred | 31% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2280,7 +2273,7 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-18% pred | 18% hist
+20% pred | 20% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2320,7 +2313,7 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 46% hist
+23% pred | 23% hist
 [DROP]</t>
         </is>
       </c>
@@ -2482,7 +2475,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-66% pred | 66% hist
+67% pred | 67% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2490,7 +2483,7 @@
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 46% hist
+47% pred | 47% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -537,7 +537,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -550,43 +550,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-55% pred | 55% hist
+58% pred | 58% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -616,7 +616,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-64% pred | 64% hist
+63% pred | 63% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -624,15 +624,15 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
+35% pred | 35% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
 36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -648,7 +648,7 @@
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Chaitanya Nahar
 9% pred | 9% hist
 [CONSIDER]</t>
         </is>
@@ -666,7 +666,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-40% pred | 40% hist
+43% pred | 43% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -797,7 +797,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-42% pred | 42% hist
+44% pred | 44% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -813,7 +813,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-31% pred | 31% hist
+30% pred | 30% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -938,7 +938,7 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-20% pred | 20% hist
+18% pred | 18% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -978,7 +978,7 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-23% pred | 23% hist
+46% pred | 46% hist
 [DROP]</t>
         </is>
       </c>
@@ -1131,8 +1131,8 @@
       <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Chaitanya Nahar
-30% pred | 30% hist
+Siddhartha Kusuma
+70% pred | 70% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1140,7 +1140,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-67% pred | 67% hist
+66% pred | 66% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1148,7 +1148,7 @@
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-47% pred | 47% hist
+46% pred | 46% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1208,7 +1208,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1221,43 +1221,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-55% pred | 55% hist
+58% pred | 58% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1287,7 +1287,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-64% pred | 64% hist
+63% pred | 63% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1295,15 +1295,15 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
+35% pred | 35% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
 36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1333,12 +1333,12 @@
         </is>
       </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Mat 57
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+43% pred | 43% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F4" s="7" t="n"/>
@@ -1468,7 +1468,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-42% pred | 42% hist
+44% pred | 44% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1480,7 +1480,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
@@ -1521,14 +1528,7 @@
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-46% pred | 46% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D11" s="7" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="9" t="inlineStr">
@@ -1555,8 +1555,8 @@
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
+          <t>Barre 57
+Chaitanya Nahar
 20% pred | 0% hist
 [EXPERIMENTAL]</t>
         </is>
@@ -1605,15 +1605,15 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+18% pred | 18% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
@@ -1649,7 +1649,7 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-23% pred | 23% hist
+46% pred | 46% hist
 [DROP]</t>
         </is>
       </c>
@@ -1662,7 +1662,14 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E16" s="7" t="n"/>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
@@ -1804,7 +1811,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-67% pred | 67% hist
+66% pred | 66% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1812,7 +1819,7 @@
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-47% pred | 47% hist
+46% pred | 46% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1872,7 +1879,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1885,43 +1892,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1950,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-55% pred | 55% hist
+58% pred | 58% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1951,7 +1958,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-64% pred | 64% hist
+63% pred | 63% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1959,15 +1966,15 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
+35% pred | 35% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
 36% pred | 36% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-38% pred | 38% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2001,7 +2008,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-40% pred | 40% hist
+43% pred | 43% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2132,7 +2139,7 @@
         <is>
           <t>FIT
 Siddhartha Kusuma
-42% pred | 42% hist
+44% pred | 44% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2148,7 +2155,7 @@
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-31% pred | 31% hist
+30% pred | 30% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2273,7 +2280,7 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-20% pred | 20% hist
+18% pred | 18% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -2313,7 +2320,7 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-23% pred | 23% hist
+46% pred | 46% hist
 [DROP]</t>
         </is>
       </c>
@@ -2475,7 +2482,7 @@
         <is>
           <t>FIT
 Pushyank Nahar
-67% pred | 67% hist
+66% pred | 66% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2483,7 +2490,7 @@
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-47% pred | 47% hist
+46% pred | 46% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -648,7 +648,7 @@
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Chaitanya Nahar
+Shruti Kulkarni
 9% pred | 9% hist
 [CONSIDER]</t>
         </is>
@@ -1131,8 +1131,8 @@
       <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Siddhartha Kusuma
-70% pred | 70% hist
+Chaitanya Nahar
+30% pred | 30% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
+          <t>Cardio Barre Plus
 Shruti Kulkarni
 9% pred | 9% hist
 [CONSIDER]</t>

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -89,12 +89,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,10 +148,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -537,7 +537,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Max Score  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Max Score  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -550,43 +550,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -598,14 +598,7 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
@@ -613,7 +606,7 @@
           <t>Cardio Barre
 Siddhartha Kusuma
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -624,44 +617,44 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-63% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-36% pred | 0% hist
-[]</t>
+36% pred | 36% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -670,8 +663,8 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-9% pred | 0% hist
-[]</t>
+9% pred | 9% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -679,16 +672,16 @@
           <t>Back Body Blaze
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -696,7 +689,7 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -705,34 +698,34 @@
         <is>
           <t>FIT
 Pushyank Nahar
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-31% pred | 0% hist
-[]</t>
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -752,8 +745,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -774,13 +767,13 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
@@ -792,42 +785,42 @@
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+14% pred | 14% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>FIT
 Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-39% pred | 0% hist
-[]</t>
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -835,8 +828,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -853,33 +846,47 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="n"/>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
+46% pred | 46% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H12" s="5" t="n"/>
@@ -901,7 +908,7 @@
           <t>Cardio Barre
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -920,8 +927,8 @@
         <is>
           <t>Barre 57
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H14" s="5" t="n"/>
@@ -934,27 +941,34 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
           <t>FIT
-Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
+Shruti Kulkarni
+34% pred | 34% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Kajol Kanchan
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -972,8 +986,8 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
@@ -994,8 +1008,8 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-32% pred | 0% hist
-[]</t>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E17" s="5" t="n"/>
@@ -1004,7 +1018,7 @@
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -1013,26 +1027,33 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[DROP]</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -1041,25 +1062,25 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pushyank Nahar
-62% pred | 0% hist
-[]</t>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F19" s="5" t="n"/>
@@ -1067,7 +1088,7 @@
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
@@ -1078,8 +1099,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E20" s="5" t="n"/>
@@ -1088,7 +1109,7 @@
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>19:15</t>
         </is>
@@ -1100,16 +1121,23 @@
         <is>
           <t>Recovery
 Pushyank Nahar
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n"/>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Siddhartha Kusuma
+21% pred | 21% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>19:30</t>
         </is>
@@ -1118,8 +1146,8 @@
         <is>
           <t>Recovery
 Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -1127,15 +1155,15 @@
           <t>Recovery
 Kajol Kanchan
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -1157,7 +1185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1173,7 +1201,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1186,43 +1214,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1234,14 +1262,7 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
@@ -1249,7 +1270,7 @@
           <t>Cardio Barre
 Siddhartha Kusuma
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -1260,54 +1281,54 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Pushyank Nahar
-63% pred | 0% hist
-[]</t>
+          <t>Cardio Barre Plus
+Pushyank Nahar
+16% pred | 16% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Shruti Kulkarni
-9% pred | 0% hist
-[]</t>
+          <t>Cardio Barre Plus
+Shruti Kulkarni
+9% pred | 9% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -1315,16 +1336,23 @@
           <t>Back Body Blaze
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -1332,7 +1360,7 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1341,34 +1369,34 @@
         <is>
           <t>FIT
 Pushyank Nahar
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-31% pred | 0% hist
-[]</t>
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -1388,8 +1416,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -1410,13 +1438,13 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
@@ -1428,42 +1456,42 @@
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+14% pred | 14% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>FIT
 Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-39% pred | 0% hist
-[]</t>
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -1471,8 +1499,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -1489,18 +1517,25 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -1514,8 +1549,8 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H12" s="5" t="n"/>
@@ -1537,7 +1572,7 @@
           <t>Cardio Barre
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -1556,8 +1591,8 @@
         <is>
           <t>Barre 57
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H14" s="5" t="n"/>
@@ -1570,18 +1605,18 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
@@ -1589,8 +1624,8 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -1608,13 +1643,20 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
@@ -1630,8 +1672,8 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-32% pred | 0% hist
-[]</t>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E17" s="5" t="n"/>
@@ -1640,7 +1682,7 @@
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -1649,17 +1691,17 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[DROP]</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -1668,7 +1710,7 @@
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -1677,107 +1719,135 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pushyank Nahar
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Chaitanya Nahar
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1793,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1809,7 +1879,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-04</t>
+          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-11</t>
         </is>
       </c>
     </row>
@@ -1822,43 +1892,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-4-May</t>
+11-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-5-May</t>
+12-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-6-May</t>
+13-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-7-May</t>
+14-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-8-May</t>
+15-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-9-May</t>
+16-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-10-May</t>
+17-May</t>
         </is>
       </c>
     </row>
@@ -1870,14 +1940,7 @@
       </c>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="5" t="n"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-13% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="6" t="inlineStr">
@@ -1885,7 +1948,7 @@
           <t>Cardio Barre
 Siddhartha Kusuma
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H3" s="5" t="n"/>
@@ -1896,44 +1959,44 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Pushyank Nahar
-63% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Pushyank Nahar
+31% pred | 31% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-36% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
@@ -1942,8 +2005,8 @@
         <is>
           <t>Cardio Barre
 Shruti Kulkarni
-9% pred | 0% hist
-[]</t>
+9% pred | 9% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -1951,16 +2014,23 @@
           <t>Back Body Blaze
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="F5" s="5" t="n"/>
@@ -1968,7 +2038,7 @@
       <c r="H5" s="5" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
@@ -1977,34 +2047,34 @@
         <is>
           <t>FIT
 Pushyank Nahar
-75% pred | 0% hist
-[]</t>
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-31% pred | 0% hist
-[]</t>
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H6" s="5" t="n"/>
@@ -2024,8 +2094,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H7" s="5" t="n"/>
@@ -2046,13 +2116,13 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PINNED]</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>10:15</t>
         </is>
@@ -2064,42 +2134,42 @@
       <c r="F9" s="5" t="n"/>
       <c r="G9" s="6" t="inlineStr">
         <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze Express
+Shruti Kulkarni
+14% pred | 14% hist
+[DROP]</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
           <t>FIT
 Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-39% pred | 0% hist
-[]</t>
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E10" s="5" t="n"/>
@@ -2107,8 +2177,8 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G10" s="5" t="n"/>
@@ -2125,18 +2195,25 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Shruti Kulkarni
-50% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>11:30</t>
         </is>
@@ -2150,8 +2227,8 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H12" s="5" t="n"/>
@@ -2173,7 +2250,7 @@
           <t>Cardio Barre
 Chaitanya Nahar
 20% pred | 0% hist
-[]</t>
+[EXPERIMENTAL]</t>
         </is>
       </c>
     </row>
@@ -2192,8 +2269,8 @@
         <is>
           <t>Barre 57
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H14" s="5" t="n"/>
@@ -2206,18 +2283,18 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>FIT
-Siddhartha Kusuma
-45% pred | 0% hist
-[]</t>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
-33% pred | 0% hist
-[]</t>
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D15" s="5" t="n"/>
@@ -2225,8 +2302,8 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-35% pred | 0% hist
-[]</t>
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="F15" s="5" t="n"/>
@@ -2244,13 +2321,20 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-47% pred | 0% hist
-[]</t>
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D16" s="5" t="n"/>
       <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
@@ -2266,8 +2350,8 @@
         <is>
           <t>Barre 57
 Siddhartha Kusuma
-32% pred | 0% hist
-[]</t>
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E17" s="5" t="n"/>
@@ -2276,7 +2360,7 @@
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
@@ -2285,17 +2369,17 @@
         <is>
           <t>Back Body Blaze
 Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
+46% pred | 46% hist
+[DROP]</t>
         </is>
       </c>
       <c r="C18" s="5" t="n"/>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Kajol Kanchan
-61% pred | 0% hist
-[]</t>
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="E18" s="5" t="n"/>
@@ -2304,7 +2388,7 @@
       <c r="H18" s="5" t="n"/>
     </row>
     <row r="19" ht="52" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>18:15</t>
         </is>
@@ -2313,107 +2397,135 @@
         <is>
           <t>Barre 57
 Kajol Kanchan
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D19" s="5" t="n"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Pushyank Nahar
-62% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="n"/>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>19:00</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="5" t="n"/>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-22% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>19:15</t>
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+22% pred | 22% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
     </row>
     <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Kajol Kanchan
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-46% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n"/>
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Chaitanya Nahar
+30% pred | 30% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -537,7 +537,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Max Score  |  Week of 2026-05-11</t>
+          <t>Kenkere House  |  Max Score  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -550,43 +550,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -620,9 +620,9 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Shruti Kulkarni
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
+Pushyank Nahar
+35% pred | 35% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -633,50 +633,78 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+35% pred | 35% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
+26% pred | 26% hist
+[CONSIDER]</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Pushyank Nahar
-36% pred | 36% hist
-[PROTECT_EXACT]</t>
+Shruti Kulkarni
+30% pred | 30% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Chaitanya Nahar
 9% pred | 9% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Shruti Kulkarni
@@ -684,33 +712,40 @@
 [EXPERIMENTAL]</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
 75% pred | 75% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+15% pred | 15% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -718,34 +753,13 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 54% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+61% pred | 61% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -754,7 +768,7 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
@@ -762,20 +776,20 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-61% pred | 61% hist
-[PINNED]</t>
-        </is>
-      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>10:15</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
@@ -783,31 +797,66 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+61% pred | 61% hist
+[PINNED]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+4% pred | 4% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Shruti Kulkarni
-14% pred | 14% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
@@ -815,7 +864,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -823,8 +872,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -832,69 +881,41 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 85% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-46% pred | 46% hist
-[CONSIDER]</t>
-        </is>
-      </c>
+      <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Kajol Kanchan
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+50% pred | 50% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -902,28 +923,56 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
@@ -931,91 +980,70 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-48% pred | 48% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-34% pred | 34% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
       <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Siddhartha Kusuma
-32% pred | 32% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1023,14 +1051,7 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-46% pred | 46% hist
-[DROP]</t>
-        </is>
-      </c>
+      <c r="B18" s="5" t="n"/>
       <c r="C18" s="5" t="n"/>
       <c r="D18" s="7" t="inlineStr">
         <is>
@@ -1041,14 +1062,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n"/>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n"/>
     </row>
@@ -1069,12 +1083,19 @@
       <c r="C19" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Pushyank Nahar
-40% pred | 40% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
+Shruti Kulkarni
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
@@ -1090,80 +1111,94 @@
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+23% pred | 23% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Barre 57
-Shruti Kulkarni
-22% pred | 22% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+          <t>Back Body Blaze Express
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Pushyank Nahar
-54% pred | 54% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-21% pred | 21% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="52" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Recovery
 Chaitanya Nahar
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Kajol Kanchan
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Siddhartha Kusuma
 46% pred | 46% hist
 [PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -1185,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1201,7 +1236,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-11</t>
+          <t>Kenkere House  |  Trainer Hours  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1214,43 +1249,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1299,14 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -1284,9 +1326,9 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Shruti Kulkarni
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
+Pushyank Nahar
+35% pred | 35% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1299,9 +1341,9 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-16% pred | 16% hist
+          <t>FIT
+Pushyank Nahar
+35% pred | 35% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1309,79 +1351,107 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
+26% pred | 26% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+30% pred | 30% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre Plus
-Shruti Kulkarni
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Chaitanya Nahar
 9% pred | 9% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
 75% pred | 75% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+15% pred | 15% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -1389,34 +1459,13 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 54% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+61% pred | 61% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -1425,7 +1474,7 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
@@ -1433,8 +1482,36 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -1443,42 +1520,56 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+4% pred | 4% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Shruti Kulkarni
-14% pred | 14% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
@@ -1486,7 +1577,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -1494,8 +1585,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -1503,41 +1594,13 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 85% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -1548,17 +1611,24 @@
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Kajol Kanchan
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+50% pred | 50% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -1566,28 +1636,70 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
@@ -1595,200 +1707,158 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-48% pred | 48% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Siddhartha Kusuma
-32% pred | 32% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n"/>
+Kajol Kanchan
+0% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-46% pred | 46% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-39% pred | 39% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Pushyank Nahar
-40% pred | 40% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+Kajol Kanchan
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-22% pred | 22% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+23% pred | 23% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
@@ -1796,58 +1866,37 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="9" t="inlineStr">
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Pushyank Nahar
-54% pred | 54% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Chaitanya Nahar
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Kajol Kanchan
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1863,7 +1912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1879,7 +1928,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-11</t>
+          <t>Kenkere House  |  Class Variety  |  Week of 2026-05-04</t>
         </is>
       </c>
     </row>
@@ -1892,43 +1941,43 @@
       <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Monday
-11-May</t>
+4-May</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Tuesday
-12-May</t>
+5-May</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Wednesday
-13-May</t>
+6-May</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>Thursday
-14-May</t>
+7-May</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Friday
-15-May</t>
+8-May</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Saturday
-16-May</t>
+9-May</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Sunday
-17-May</t>
+10-May</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1991,14 @@
       <c r="C3" s="5" t="n"/>
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
@@ -1962,9 +2018,9 @@
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Shruti Kulkarni
-49% pred | 49% hist
-[PROTECT_EXACT]</t>
+Pushyank Nahar
+35% pred | 35% hist
+[PINNED]</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
@@ -1977,9 +2033,9 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Pushyank Nahar
-31% pred | 31% hist
+          <t>FIT
+Pushyank Nahar
+35% pred | 35% hist
 [CONSIDER]</t>
         </is>
       </c>
@@ -1987,79 +2043,107 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="n"/>
+26% pred | 26% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+30% pred | 30% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n"/>
     </row>
     <row r="5" ht="52" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>08:30</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Cardio Barre
-Shruti Kulkarni
+Chaitanya Nahar
 9% pred | 9% hist
 [CONSIDER]</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Back Body Blaze
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>FIT
 Pushyank Nahar
 75% pred | 75% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 29% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+15% pred | 15% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Pushyank Nahar
@@ -2067,34 +2151,13 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 54% hist
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+61% pred | 61% hist
 [PROTECT_EXACT]</t>
         </is>
       </c>
@@ -2103,7 +2166,7 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="B8" s="5" t="n"/>
@@ -2111,8 +2174,36 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -2121,42 +2212,56 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Pushyank Nahar
-44% pred | 44% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-    </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+4% pred | 4% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze Express
-Shruti Kulkarni
-14% pred | 14% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+29% pred | 29% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>FIT
 Siddhartha Kusuma
@@ -2164,7 +2269,7 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Mat 57
 Pushyank Nahar
@@ -2172,8 +2277,8 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
@@ -2181,41 +2286,13 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n"/>
-      <c r="H10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>11:15</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-85% pred | 85% hist
-[PINNED]</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-31% pred | 31% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="5" t="n"/>
@@ -2226,17 +2303,24 @@
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Kajol Kanchan
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="n"/>
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+50% pred | 50% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>12:30</t>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B13" s="5" t="n"/>
@@ -2244,28 +2328,70 @@
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Chaitanya Nahar
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n"/>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="5" t="n"/>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Barre 57
 Chaitanya Nahar
@@ -2273,200 +2399,158 @@
 [PROTECT_EXACT]</t>
         </is>
       </c>
-      <c r="H14" s="5" t="n"/>
-    </row>
-    <row r="15" ht="52" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Kajol Kanchan
-48% pred | 48% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 35% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="n"/>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-47% pred | 47% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 33% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="n"/>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C17" s="5" t="n"/>
       <c r="D17" s="6" t="inlineStr">
         <is>
           <t>Barre 57
-Siddhartha Kusuma
-32% pred | 32% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="n"/>
+Kajol Kanchan
+0% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+35% pred | 35% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-46% pred | 46% hist
-[DROP]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Kajol Kanchan
-61% pred | 61% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
-      <c r="H18" s="5" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-39% pred | 39% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Mat 57
-Pushyank Nahar
-40% pred | 40% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 38% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>FIT
-Kajol Kanchan
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
+Kajol Kanchan
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n"/>
     </row>
     <row r="20" ht="52" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Pushyank Nahar
-30% pred | 30% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+42% pred | 42% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
       <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n"/>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-22% pred | 22% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+0% pred | 0% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="F21" s="5" t="n"/>
       <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n"/>
@@ -2474,58 +2558,37 @@
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="9" t="inlineStr">
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Recovery
-Pushyank Nahar
-54% pred | 54% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
       <c r="F22" s="5" t="n"/>
       <c r="G22" s="5" t="n"/>
       <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="52" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Chaitanya Nahar
-30% pred | 30% hist
-[CONSIDER]</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Kajol Kanchan
-20% pred | 0% hist
-[EXPERIMENTAL]</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Mat 57
-Siddhartha Kusuma
-46% pred | 46% hist
-[PROTECT_EXACT]</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/outputs/schedule_kenkere.xlsx
+++ b/outputs/schedule_kenkere.xlsx
@@ -47,13 +47,13 @@
       <sz val="9"/>
     </font>
     <font>
+      <color rgb="000C4A6E"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="0092400E"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <color rgb="000C4A6E"/>
-      <sz val="9"/>
     </font>
     <font>
       <color rgb="00065F46"/>
@@ -89,12 +89,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00D5F2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5F2F8"/>
+        <fgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
     <fill>
@@ -148,10 +148,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -598,17 +598,31 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-12% pred | 0% hist
-[]</t>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -617,30 +631,44 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+35% pred | 35% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-26% pred | 0% hist
-[]</t>
+26% pred | 26% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
@@ -649,90 +677,97 @@
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+57% pred | 57% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-57% pred | 0% hist
-[]</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -740,7 +775,7 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -748,111 +783,118 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -863,38 +905,52 @@
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
@@ -902,120 +958,253 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+36% pred | 36% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+66% pred | 66% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1031,7 +1220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1108,17 +1297,31 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-12% pred | 0% hist
-[]</t>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -1127,13 +1330,20 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D4" s="6" t="n"/>
@@ -1141,16 +1351,16 @@
         <is>
           <t>Barre 57
 Shruti Kulkarni
-26% pred | 0% hist
-[]</t>
+26% pred | 26% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
@@ -1159,90 +1369,97 @@
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+57% pred | 57% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-57% pred | 0% hist
-[]</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -1250,7 +1467,7 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -1258,111 +1475,118 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -1373,126 +1597,154 @@
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
       <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="C15" s="6" t="n"/>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E15" s="6" t="n"/>
       <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="H15" s="6" t="n"/>
     </row>
     <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-40% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 0% hist
-[]</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+39% pred | 39% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+36% pred | 36% hist
+[INCLUDE]</t>
         </is>
       </c>
       <c r="F17" s="6" t="n"/>
@@ -1500,25 +1752,18 @@
       <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>FIT
-Pushyank Nahar
-66% pred | 0% hist
-[]</t>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
@@ -1526,6 +1771,160 @@
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+66% pred | 66% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1541,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1618,17 +2017,31 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre Plus
-Pushyank Nahar
-12% pred | 0% hist
-[]</t>
+          <t>FIT
+Pushyank Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="C3" s="6" t="n"/>
       <c r="D3" s="6" t="n"/>
       <c r="E3" s="6" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="H3" s="6" t="n"/>
     </row>
     <row r="4" ht="52" customHeight="1">
@@ -1637,30 +2050,44 @@
           <t>07:15</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Cardio Barre
 Siddhartha Kusuma
-58% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
+58% pred | 58% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+35% pred | 35% hist
+[CONSIDER]</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-26% pred | 0% hist
-[]</t>
+26% pred | 26% hist
+[PROTECT]</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Barre 57
 Shruti Kulkarni
-30% pred | 0% hist
-[]</t>
+30% pred | 30% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
@@ -1669,90 +2096,104 @@
     <row r="5" ht="52" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Cardio Barre
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Cardio Barre
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
         </is>
       </c>
       <c r="H5" s="6" t="n"/>
     </row>
     <row r="6" ht="52" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+75% pred | 75% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
-Siddhartha Kusuma
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Shruti Kulkarni
-0% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+31% pred | 31% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n"/>
       <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+57% pred | 57% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="n"/>
     </row>
     <row r="7" ht="52" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-75% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-31% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
       <c r="E7" s="6" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-57% pred | 0% hist
-[]</t>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H7" s="6" t="n"/>
@@ -1760,7 +2201,7 @@
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B8" s="6" t="n"/>
@@ -1768,111 +2209,118 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-54% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+56% pred | 56% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="52" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>10:15</t>
         </is>
       </c>
       <c r="B9" s="6" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Chaitanya Nahar
-56% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Pushyank Nahar
+44% pred | 44% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="n"/>
     </row>
     <row r="10" ht="52" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Shruti Kulkarni
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-84% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+35% pred | 35% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Shruti Kulkarni
+29% pred | 29% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="6" t="n"/>
     </row>
     <row r="11" ht="52" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Siddhartha Kusuma
-44% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-39% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-29% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+85% pred | 85% hist
+[PINNED]</t>
+        </is>
+      </c>
       <c r="H11" s="6" t="n"/>
     </row>
     <row r="12" ht="52" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>11:15</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B12" s="6" t="n"/>
@@ -1883,38 +2331,52 @@
       <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Barre 57
-Pushyank Nahar
-85% pred | 0% hist
-[]</t>
+Shruti Kulkarni
+49% pred | 49% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
     </row>
     <row r="13" ht="52" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Shruti Kulkarni
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Shruti Kulkarni
-49% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n"/>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Kajol Kanchan
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B14" s="6" t="n"/>
@@ -1922,120 +2384,260 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Chaitanya Nahar
-20% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+50% pred | 50% hist
+[CONSIDER]</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="n"/>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Chaitanya Nahar
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Chaitanya Nahar
+28% pred | 28% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Pushyank Nahar
-33% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Barre 57
-Kajol Kanchan
-35% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Back Body Blaze
+          <t>FIT
 Chaitanya Nahar
-28% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="n"/>
+45% pred | 45% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Pushyank Nahar
+33% pred | 33% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+36% pred | 36% hist
+[INCLUDE]</t>
+        </is>
+      </c>
       <c r="F16" s="6" t="n"/>
       <c r="G16" s="6" t="n"/>
       <c r="H16" s="6" t="n"/>
     </row>
     <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>18:15</t>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>17:15</t>
         </is>
       </c>
       <c r="B17" s="6" t="n"/>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Mat 57
-Pushyank Nahar
-40% pred | 0% hist
-[]</t>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+47% pred | 47% hist
+[PROTECT_EXACT]</t>
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Back Body Blaze
-Kajol Kanchan
-38% pred | 0% hist
-[]</t>
-        </is>
-      </c>
+      <c r="E17" s="6" t="n"/>
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="6" t="n"/>
       <c r="H17" s="6" t="n"/>
     </row>
     <row r="18" ht="52" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>Recovery
-Chaitanya Nahar
-30% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>FIT
-Pushyank Nahar
-66% pred | 0% hist
-[]</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Siddhartha Kusuma
+32% pred | 32% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
       <c r="E18" s="6" t="n"/>
       <c r="F18" s="6" t="n"/>
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Chaitanya Nahar
+28% pred | 28% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Kajol Kanchan
+61% pred | 61% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+39% pred | 39% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Pushyank Nahar
+40% pred | 40% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Back Body Blaze
+Kajol Kanchan
+38% pred | 38% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+27% pred | 27% hist
+[INCLUDE]</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Pushyank Nahar
+54% pred | 54% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Recovery
+Siddhartha Kusuma
+20% pred | 0% hist
+[EXPERIMENTAL]</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Barre 57
+Kajol Kanchan
+48% pred | 48% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>FIT
+Pushyank Nahar
+66% pred | 66% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>Mat 57
+Siddhartha Kusuma
+46% pred | 46% hist
+[PROTECT_EXACT]</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
